--- a/public/bulk-upload-template.xlsx
+++ b/public/bulk-upload-template.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -435,6 +435,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -473,6 +474,11 @@
           <t>preferred_contact</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>visibility</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -508,6 +514,11 @@
           <t>email</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -543,6 +554,11 @@
           <t>both</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -578,9 +594,14 @@
           <t>phone</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <dataValidations count="3">
+  <dataValidations count="4">
     <dataValidation sqref="C2:C500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>Lists!$A$1:$A$62</formula1>
     </dataValidation>
@@ -589,6 +610,9 @@
     </dataValidation>
     <dataValidation sqref="G2:G500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>Lists!$C$1:$C$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="H2:H500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>Lists!$D$1:$D$2</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -601,7 +625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C62"/>
+  <dimension ref="A1:D62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -620,6 +644,11 @@
           <t>email</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -635,6 +664,11 @@
       <c r="C2" t="inlineStr">
         <is>
           <t>phone</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>group</t>
         </is>
       </c>
     </row>
